--- a/media/template_excel/Template_Data_Siswa.xlsx
+++ b/media/template_excel/Template_Data_Siswa.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr showInkAnnotation="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\adminsekolah\master-as\media\template_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{5FCFBBC6-BD3B-442D-9847-815228EE9B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D71AD1ED-57DF-4F84-83F6-268A7C87A824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" xr2:uid="{7BD0FB70-41CC-43CC-94E6-C47B4BB57B73}"/>
   </bookViews>
@@ -16,15 +16,6 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="144525" concurrentCalc="0"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -114,7 +105,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -291,7 +282,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -303,94 +294,87 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
-    <xf numFmtId="179" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -745,7 +729,7 @@
     <col min="5" max="5" width="12.5" customWidth="1"/>
     <col min="6" max="6" width="21.375" customWidth="1"/>
     <col min="7" max="8" width="17.125" customWidth="1"/>
-    <col min="9" max="9" width="17.125" style="45" customWidth="1"/>
+    <col min="9" max="9" width="17.125" style="40" customWidth="1"/>
     <col min="10" max="11" width="17.125" customWidth="1"/>
     <col min="12" max="12" width="56.375" style="2" customWidth="1"/>
     <col min="13" max="13" width="34" customWidth="1"/>
@@ -778,7 +762,7 @@
       <c r="H1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="I1" s="41" t="s">
+      <c r="I1" s="36" t="s">
         <v>12</v>
       </c>
       <c r="J1" s="4" t="s">
@@ -798,57 +782,57 @@
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="38" t="s">
+      <c r="C2" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="38" t="s">
+      <c r="D2" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="38" t="s">
+      <c r="E2" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="38" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" s="39" t="s">
+      <c r="F2" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="39" t="s">
+      <c r="G2" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="42" t="s">
+      <c r="H2" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="39" t="s">
+      <c r="I2" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="39" t="s">
+      <c r="J2" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="L2" s="39" t="s">
+      <c r="K2" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="M2" s="39" t="s">
+      <c r="L2" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="N2" s="39" t="s">
+      <c r="M2" s="34" t="s">
         <v>8</v>
       </c>
+      <c r="N2" s="34" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="33">
+      <c r="A3" s="28">
         <v>2018011</v>
       </c>
-      <c r="B3" s="48" t="s">
+      <c r="B3" s="43" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="46" t="s">
+      <c r="C3" s="41" t="s">
         <v>23</v>
       </c>
       <c r="D3" s="8">
@@ -857,31 +841,31 @@
       <c r="E3" s="8">
         <v>2</v>
       </c>
-      <c r="F3" s="40" t="s">
+      <c r="F3" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="35" t="s">
+      <c r="G3" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="36" t="s">
+      <c r="H3" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="43">
+      <c r="I3" s="38">
         <v>39204</v>
       </c>
-      <c r="J3" s="36" t="s">
+      <c r="J3" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="47" t="s">
+      <c r="K3" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="L3" s="37" t="s">
+      <c r="L3" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="M3" s="34" t="s">
+      <c r="M3" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="N3" s="37" t="s">
+      <c r="N3" s="32" t="s">
         <v>17</v>
       </c>
     </row>
@@ -894,13 +878,13 @@
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
-      <c r="I4" s="44"/>
+      <c r="I4" s="39"/>
       <c r="J4" s="8"/>
       <c r="K4" s="8"/>
       <c r="L4" s="14"/>
       <c r="M4" s="7"/>
       <c r="N4" s="15"/>
-      <c r="O4" s="21"/>
+      <c r="O4" s="18"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="6"/>
@@ -911,13 +895,13 @@
       <c r="F5" s="8"/>
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
-      <c r="I5" s="44"/>
+      <c r="I5" s="39"/>
       <c r="J5" s="8"/>
       <c r="K5" s="8"/>
       <c r="L5" s="14"/>
       <c r="M5" s="7"/>
       <c r="N5" s="15"/>
-      <c r="O5" s="21"/>
+      <c r="O5" s="18"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
@@ -928,13 +912,13 @@
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
-      <c r="I6" s="44"/>
+      <c r="I6" s="39"/>
       <c r="J6" s="8"/>
       <c r="K6" s="8"/>
       <c r="L6" s="14"/>
       <c r="M6" s="7"/>
       <c r="N6" s="15"/>
-      <c r="O6" s="21"/>
+      <c r="O6" s="18"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="6"/>
@@ -945,13 +929,13 @@
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
-      <c r="I7" s="44"/>
+      <c r="I7" s="39"/>
       <c r="J7" s="8"/>
       <c r="K7" s="8"/>
       <c r="L7" s="14"/>
       <c r="M7" s="7"/>
       <c r="N7" s="15"/>
-      <c r="O7" s="21"/>
+      <c r="O7" s="18"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="6"/>
@@ -962,13 +946,13 @@
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
-      <c r="I8" s="44"/>
+      <c r="I8" s="39"/>
       <c r="J8" s="8"/>
       <c r="K8" s="8"/>
       <c r="L8" s="14"/>
       <c r="M8" s="7"/>
       <c r="N8" s="15"/>
-      <c r="O8" s="21"/>
+      <c r="O8" s="18"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="6"/>
@@ -979,13 +963,13 @@
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
       <c r="H9" s="8"/>
-      <c r="I9" s="44"/>
+      <c r="I9" s="39"/>
       <c r="J9" s="8"/>
       <c r="K9" s="8"/>
       <c r="L9" s="14"/>
       <c r="M9" s="7"/>
       <c r="N9" s="15"/>
-      <c r="O9" s="21"/>
+      <c r="O9" s="18"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
@@ -996,13 +980,13 @@
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
       <c r="H10" s="8"/>
-      <c r="I10" s="44"/>
+      <c r="I10" s="39"/>
       <c r="J10" s="8"/>
       <c r="K10" s="8"/>
       <c r="L10" s="14"/>
       <c r="M10" s="7"/>
       <c r="N10" s="15"/>
-      <c r="O10" s="21"/>
+      <c r="O10" s="18"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="6"/>
@@ -1013,13 +997,13 @@
       <c r="F11" s="8"/>
       <c r="G11" s="8"/>
       <c r="H11" s="8"/>
-      <c r="I11" s="44"/>
+      <c r="I11" s="39"/>
       <c r="J11" s="8"/>
       <c r="K11" s="8"/>
       <c r="L11" s="14"/>
       <c r="M11" s="7"/>
       <c r="N11" s="15"/>
-      <c r="O11" s="21"/>
+      <c r="O11" s="18"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="6"/>
@@ -1030,13 +1014,13 @@
       <c r="F12" s="8"/>
       <c r="G12" s="8"/>
       <c r="H12" s="8"/>
-      <c r="I12" s="44"/>
+      <c r="I12" s="39"/>
       <c r="J12" s="8"/>
       <c r="K12" s="8"/>
       <c r="L12" s="14"/>
       <c r="M12" s="7"/>
       <c r="N12" s="15"/>
-      <c r="O12" s="21"/>
+      <c r="O12" s="18"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="6"/>
@@ -1047,13 +1031,13 @@
       <c r="F13" s="8"/>
       <c r="G13" s="8"/>
       <c r="H13" s="8"/>
-      <c r="I13" s="44"/>
+      <c r="I13" s="39"/>
       <c r="J13" s="8"/>
       <c r="K13" s="8"/>
       <c r="L13" s="14"/>
       <c r="M13" s="7"/>
       <c r="N13" s="15"/>
-      <c r="O13" s="21"/>
+      <c r="O13" s="18"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="6"/>
@@ -1064,13 +1048,13 @@
       <c r="F14" s="8"/>
       <c r="G14" s="8"/>
       <c r="H14" s="8"/>
-      <c r="I14" s="44"/>
+      <c r="I14" s="39"/>
       <c r="J14" s="8"/>
       <c r="K14" s="8"/>
       <c r="L14" s="14"/>
       <c r="M14" s="7"/>
       <c r="N14" s="15"/>
-      <c r="O14" s="21"/>
+      <c r="O14" s="18"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="6"/>
@@ -1081,13 +1065,13 @@
       <c r="F15" s="8"/>
       <c r="G15" s="8"/>
       <c r="H15" s="8"/>
-      <c r="I15" s="44"/>
+      <c r="I15" s="39"/>
       <c r="J15" s="8"/>
       <c r="K15" s="8"/>
       <c r="L15" s="14"/>
       <c r="M15" s="7"/>
       <c r="N15" s="15"/>
-      <c r="O15" s="21"/>
+      <c r="O15" s="18"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
@@ -1098,13 +1082,13 @@
       <c r="F16" s="8"/>
       <c r="G16" s="8"/>
       <c r="H16" s="8"/>
-      <c r="I16" s="44"/>
+      <c r="I16" s="39"/>
       <c r="J16" s="8"/>
       <c r="K16" s="8"/>
       <c r="L16" s="14"/>
       <c r="M16" s="7"/>
       <c r="N16" s="15"/>
-      <c r="O16" s="21"/>
+      <c r="O16" s="18"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="6"/>
@@ -1115,13 +1099,13 @@
       <c r="F17" s="8"/>
       <c r="G17" s="8"/>
       <c r="H17" s="8"/>
-      <c r="I17" s="44"/>
+      <c r="I17" s="39"/>
       <c r="J17" s="8"/>
       <c r="K17" s="8"/>
       <c r="L17" s="14"/>
       <c r="M17" s="7"/>
       <c r="N17" s="15"/>
-      <c r="O17" s="21"/>
+      <c r="O17" s="18"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="6"/>
@@ -1132,13 +1116,13 @@
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
       <c r="H18" s="8"/>
-      <c r="I18" s="44"/>
+      <c r="I18" s="39"/>
       <c r="J18" s="8"/>
       <c r="K18" s="8"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="17"/>
-      <c r="N18" s="18"/>
-      <c r="O18" s="22"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="15"/>
+      <c r="O18" s="18"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="6"/>
@@ -1149,13 +1133,13 @@
       <c r="F19" s="8"/>
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
-      <c r="I19" s="44"/>
+      <c r="I19" s="39"/>
       <c r="J19" s="8"/>
       <c r="K19" s="8"/>
       <c r="L19" s="14"/>
       <c r="M19" s="7"/>
       <c r="N19" s="15"/>
-      <c r="O19" s="21"/>
+      <c r="O19" s="18"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="6"/>
@@ -1166,13 +1150,13 @@
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
       <c r="H20" s="8"/>
-      <c r="I20" s="44"/>
+      <c r="I20" s="39"/>
       <c r="J20" s="8"/>
       <c r="K20" s="8"/>
       <c r="L20" s="14"/>
       <c r="M20" s="7"/>
       <c r="N20" s="15"/>
-      <c r="O20" s="21"/>
+      <c r="O20" s="18"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="6"/>
@@ -1183,13 +1167,13 @@
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
       <c r="H21" s="8"/>
-      <c r="I21" s="44"/>
+      <c r="I21" s="39"/>
       <c r="J21" s="8"/>
       <c r="K21" s="8"/>
       <c r="L21" s="14"/>
       <c r="M21" s="7"/>
       <c r="N21" s="15"/>
-      <c r="O21" s="21"/>
+      <c r="O21" s="18"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="6"/>
@@ -1200,13 +1184,13 @@
       <c r="F22" s="8"/>
       <c r="G22" s="8"/>
       <c r="H22" s="8"/>
-      <c r="I22" s="44"/>
+      <c r="I22" s="39"/>
       <c r="J22" s="8"/>
       <c r="K22" s="8"/>
       <c r="L22" s="14"/>
       <c r="M22" s="7"/>
       <c r="N22" s="15"/>
-      <c r="O22" s="21"/>
+      <c r="O22" s="18"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="6"/>
@@ -1217,13 +1201,13 @@
       <c r="F23" s="8"/>
       <c r="G23" s="8"/>
       <c r="H23" s="8"/>
-      <c r="I23" s="44"/>
+      <c r="I23" s="39"/>
       <c r="J23" s="8"/>
       <c r="K23" s="8"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="17"/>
-      <c r="N23" s="18"/>
-      <c r="O23" s="23"/>
+      <c r="L23" s="14"/>
+      <c r="M23" s="7"/>
+      <c r="N23" s="15"/>
+      <c r="O23" s="19"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="6"/>
@@ -1234,13 +1218,13 @@
       <c r="F24" s="8"/>
       <c r="G24" s="8"/>
       <c r="H24" s="8"/>
-      <c r="I24" s="44"/>
+      <c r="I24" s="39"/>
       <c r="J24" s="8"/>
       <c r="K24" s="8"/>
       <c r="L24" s="14"/>
       <c r="M24" s="7"/>
       <c r="N24" s="15"/>
-      <c r="O24" s="21"/>
+      <c r="O24" s="18"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="6"/>
@@ -1251,13 +1235,13 @@
       <c r="F25" s="8"/>
       <c r="G25" s="8"/>
       <c r="H25" s="8"/>
-      <c r="I25" s="44"/>
+      <c r="I25" s="39"/>
       <c r="J25" s="8"/>
       <c r="K25" s="8"/>
       <c r="L25" s="14"/>
       <c r="M25" s="7"/>
       <c r="N25" s="15"/>
-      <c r="O25" s="21"/>
+      <c r="O25" s="18"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="6"/>
@@ -1268,13 +1252,13 @@
       <c r="F26" s="8"/>
       <c r="G26" s="8"/>
       <c r="H26" s="8"/>
-      <c r="I26" s="44"/>
+      <c r="I26" s="39"/>
       <c r="J26" s="8"/>
       <c r="K26" s="8"/>
       <c r="L26" s="14"/>
       <c r="M26" s="7"/>
       <c r="N26" s="15"/>
-      <c r="O26" s="21"/>
+      <c r="O26" s="18"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="6"/>
@@ -1285,13 +1269,13 @@
       <c r="F27" s="8"/>
       <c r="G27" s="8"/>
       <c r="H27" s="8"/>
-      <c r="I27" s="44"/>
+      <c r="I27" s="39"/>
       <c r="J27" s="8"/>
       <c r="K27" s="8"/>
       <c r="L27" s="14"/>
       <c r="M27" s="7"/>
       <c r="N27" s="15"/>
-      <c r="O27" s="21"/>
+      <c r="O27" s="18"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="6"/>
@@ -1302,13 +1286,13 @@
       <c r="F28" s="8"/>
       <c r="G28" s="8"/>
       <c r="H28" s="8"/>
-      <c r="I28" s="44"/>
+      <c r="I28" s="39"/>
       <c r="J28" s="8"/>
       <c r="K28" s="8"/>
       <c r="L28" s="14"/>
       <c r="M28" s="7"/>
       <c r="N28" s="15"/>
-      <c r="O28" s="21"/>
+      <c r="O28" s="18"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="6"/>
@@ -1319,13 +1303,13 @@
       <c r="F29" s="8"/>
       <c r="G29" s="8"/>
       <c r="H29" s="8"/>
-      <c r="I29" s="44"/>
+      <c r="I29" s="39"/>
       <c r="J29" s="8"/>
       <c r="K29" s="8"/>
       <c r="L29" s="14"/>
       <c r="M29" s="7"/>
       <c r="N29" s="15"/>
-      <c r="O29" s="21"/>
+      <c r="O29" s="18"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="6"/>
@@ -1336,13 +1320,13 @@
       <c r="F30" s="8"/>
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
-      <c r="I30" s="44"/>
+      <c r="I30" s="39"/>
       <c r="J30" s="8"/>
       <c r="K30" s="8"/>
       <c r="L30" s="14"/>
       <c r="M30" s="7"/>
       <c r="N30" s="15"/>
-      <c r="O30" s="21"/>
+      <c r="O30" s="18"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="6"/>
@@ -1353,13 +1337,13 @@
       <c r="F31" s="8"/>
       <c r="G31" s="8"/>
       <c r="H31" s="8"/>
-      <c r="I31" s="44"/>
+      <c r="I31" s="39"/>
       <c r="J31" s="8"/>
       <c r="K31" s="8"/>
       <c r="L31" s="14"/>
       <c r="M31" s="7"/>
       <c r="N31" s="15"/>
-      <c r="O31" s="21"/>
+      <c r="O31" s="18"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="10"/>
@@ -1370,13 +1354,13 @@
       <c r="F32" s="8"/>
       <c r="G32" s="8"/>
       <c r="H32" s="8"/>
-      <c r="I32" s="44"/>
+      <c r="I32" s="39"/>
       <c r="J32" s="8"/>
       <c r="K32" s="8"/>
       <c r="L32" s="14"/>
       <c r="M32" s="7"/>
       <c r="N32" s="15"/>
-      <c r="O32" s="21"/>
+      <c r="O32" s="18"/>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="10"/>
@@ -1387,13 +1371,13 @@
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="8"/>
-      <c r="I33" s="44"/>
+      <c r="I33" s="39"/>
       <c r="J33" s="8"/>
       <c r="K33" s="8"/>
-      <c r="L33" s="19"/>
+      <c r="L33" s="16"/>
       <c r="M33" s="11"/>
-      <c r="N33" s="20"/>
-      <c r="O33" s="24"/>
+      <c r="N33" s="17"/>
+      <c r="O33" s="20"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="10"/>
@@ -1404,13 +1388,13 @@
       <c r="F34" s="8"/>
       <c r="G34" s="8"/>
       <c r="H34" s="8"/>
-      <c r="I34" s="44"/>
+      <c r="I34" s="39"/>
       <c r="J34" s="8"/>
       <c r="K34" s="8"/>
       <c r="L34" s="14"/>
       <c r="M34" s="7"/>
       <c r="N34" s="15"/>
-      <c r="O34" s="21"/>
+      <c r="O34" s="18"/>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="10"/>
@@ -1421,13 +1405,13 @@
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="8"/>
-      <c r="I35" s="44"/>
+      <c r="I35" s="39"/>
       <c r="J35" s="8"/>
       <c r="K35" s="8"/>
       <c r="L35" s="14"/>
       <c r="M35" s="7"/>
       <c r="N35" s="15"/>
-      <c r="O35" s="21"/>
+      <c r="O35" s="18"/>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="10"/>
@@ -1438,13 +1422,13 @@
       <c r="F36" s="8"/>
       <c r="G36" s="8"/>
       <c r="H36" s="8"/>
-      <c r="I36" s="44"/>
+      <c r="I36" s="39"/>
       <c r="J36" s="8"/>
       <c r="K36" s="8"/>
       <c r="L36" s="14"/>
       <c r="M36" s="7"/>
       <c r="N36" s="15"/>
-      <c r="O36" s="21"/>
+      <c r="O36" s="18"/>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="10"/>
@@ -1455,13 +1439,13 @@
       <c r="F37" s="8"/>
       <c r="G37" s="8"/>
       <c r="H37" s="8"/>
-      <c r="I37" s="44"/>
+      <c r="I37" s="39"/>
       <c r="J37" s="8"/>
       <c r="K37" s="8"/>
       <c r="L37" s="14"/>
       <c r="M37" s="7"/>
       <c r="N37" s="15"/>
-      <c r="O37" s="21"/>
+      <c r="O37" s="18"/>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="10"/>
@@ -1472,13 +1456,13 @@
       <c r="F38" s="8"/>
       <c r="G38" s="8"/>
       <c r="H38" s="8"/>
-      <c r="I38" s="44"/>
+      <c r="I38" s="39"/>
       <c r="J38" s="8"/>
       <c r="K38" s="8"/>
-      <c r="L38" s="19"/>
+      <c r="L38" s="16"/>
       <c r="M38" s="11"/>
-      <c r="N38" s="20"/>
-      <c r="O38" s="24"/>
+      <c r="N38" s="17"/>
+      <c r="O38" s="20"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="10"/>
@@ -1489,13 +1473,13 @@
       <c r="F39" s="8"/>
       <c r="G39" s="8"/>
       <c r="H39" s="8"/>
-      <c r="I39" s="44"/>
+      <c r="I39" s="39"/>
       <c r="J39" s="8"/>
       <c r="K39" s="8"/>
-      <c r="L39" s="19"/>
+      <c r="L39" s="16"/>
       <c r="M39" s="11"/>
-      <c r="N39" s="20"/>
-      <c r="O39" s="24"/>
+      <c r="N39" s="17"/>
+      <c r="O39" s="20"/>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="10"/>
@@ -1506,13 +1490,13 @@
       <c r="F40" s="8"/>
       <c r="G40" s="8"/>
       <c r="H40" s="8"/>
-      <c r="I40" s="44"/>
+      <c r="I40" s="39"/>
       <c r="J40" s="8"/>
       <c r="K40" s="8"/>
       <c r="L40" s="14"/>
       <c r="M40" s="7"/>
       <c r="N40" s="15"/>
-      <c r="O40" s="21"/>
+      <c r="O40" s="18"/>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="10"/>
@@ -1523,13 +1507,13 @@
       <c r="F41" s="8"/>
       <c r="G41" s="8"/>
       <c r="H41" s="8"/>
-      <c r="I41" s="44"/>
+      <c r="I41" s="39"/>
       <c r="J41" s="8"/>
       <c r="K41" s="8"/>
       <c r="L41" s="14"/>
       <c r="M41" s="7"/>
       <c r="N41" s="15"/>
-      <c r="O41" s="21"/>
+      <c r="O41" s="18"/>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="10"/>
@@ -1540,13 +1524,13 @@
       <c r="F42" s="8"/>
       <c r="G42" s="8"/>
       <c r="H42" s="8"/>
-      <c r="I42" s="44"/>
+      <c r="I42" s="39"/>
       <c r="J42" s="8"/>
       <c r="K42" s="8"/>
-      <c r="L42" s="19"/>
+      <c r="L42" s="16"/>
       <c r="M42" s="11"/>
-      <c r="N42" s="20"/>
-      <c r="O42" s="24"/>
+      <c r="N42" s="17"/>
+      <c r="O42" s="20"/>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="10"/>
@@ -1557,13 +1541,13 @@
       <c r="F43" s="8"/>
       <c r="G43" s="8"/>
       <c r="H43" s="8"/>
-      <c r="I43" s="44"/>
+      <c r="I43" s="39"/>
       <c r="J43" s="8"/>
       <c r="K43" s="8"/>
       <c r="L43" s="14"/>
       <c r="M43" s="7"/>
       <c r="N43" s="15"/>
-      <c r="O43" s="21"/>
+      <c r="O43" s="18"/>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="10"/>
@@ -1574,13 +1558,13 @@
       <c r="F44" s="8"/>
       <c r="G44" s="8"/>
       <c r="H44" s="8"/>
-      <c r="I44" s="44"/>
+      <c r="I44" s="39"/>
       <c r="J44" s="8"/>
       <c r="K44" s="8"/>
       <c r="L44" s="14"/>
       <c r="M44" s="7"/>
       <c r="N44" s="15"/>
-      <c r="O44" s="21"/>
+      <c r="O44" s="18"/>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="10"/>
@@ -1591,13 +1575,13 @@
       <c r="F45" s="8"/>
       <c r="G45" s="8"/>
       <c r="H45" s="8"/>
-      <c r="I45" s="44"/>
+      <c r="I45" s="39"/>
       <c r="J45" s="8"/>
       <c r="K45" s="8"/>
-      <c r="L45" s="19"/>
+      <c r="L45" s="16"/>
       <c r="M45" s="11"/>
-      <c r="N45" s="20"/>
-      <c r="O45" s="24"/>
+      <c r="N45" s="17"/>
+      <c r="O45" s="20"/>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="10"/>
@@ -1608,13 +1592,13 @@
       <c r="F46" s="8"/>
       <c r="G46" s="8"/>
       <c r="H46" s="8"/>
-      <c r="I46" s="44"/>
+      <c r="I46" s="39"/>
       <c r="J46" s="8"/>
       <c r="K46" s="8"/>
       <c r="L46" s="14"/>
       <c r="M46" s="7"/>
       <c r="N46" s="15"/>
-      <c r="O46" s="21"/>
+      <c r="O46" s="18"/>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="10"/>
@@ -1625,13 +1609,13 @@
       <c r="F47" s="8"/>
       <c r="G47" s="8"/>
       <c r="H47" s="8"/>
-      <c r="I47" s="44"/>
+      <c r="I47" s="39"/>
       <c r="J47" s="8"/>
       <c r="K47" s="8"/>
       <c r="L47" s="14"/>
       <c r="M47" s="7"/>
       <c r="N47" s="15"/>
-      <c r="O47" s="21"/>
+      <c r="O47" s="18"/>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="10"/>
@@ -1642,13 +1626,13 @@
       <c r="F48" s="8"/>
       <c r="G48" s="8"/>
       <c r="H48" s="8"/>
-      <c r="I48" s="44"/>
+      <c r="I48" s="39"/>
       <c r="J48" s="8"/>
       <c r="K48" s="8"/>
       <c r="L48" s="14"/>
       <c r="M48" s="7"/>
       <c r="N48" s="15"/>
-      <c r="O48" s="21"/>
+      <c r="O48" s="18"/>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="10"/>
@@ -1659,13 +1643,13 @@
       <c r="F49" s="8"/>
       <c r="G49" s="8"/>
       <c r="H49" s="8"/>
-      <c r="I49" s="44"/>
+      <c r="I49" s="39"/>
       <c r="J49" s="8"/>
       <c r="K49" s="8"/>
       <c r="L49" s="14"/>
       <c r="M49" s="7"/>
       <c r="N49" s="15"/>
-      <c r="O49" s="21"/>
+      <c r="O49" s="18"/>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="10"/>
@@ -1676,13 +1660,13 @@
       <c r="F50" s="8"/>
       <c r="G50" s="8"/>
       <c r="H50" s="8"/>
-      <c r="I50" s="44"/>
+      <c r="I50" s="39"/>
       <c r="J50" s="8"/>
       <c r="K50" s="8"/>
-      <c r="L50" s="19"/>
+      <c r="L50" s="16"/>
       <c r="M50" s="11"/>
-      <c r="N50" s="20"/>
-      <c r="O50" s="24"/>
+      <c r="N50" s="17"/>
+      <c r="O50" s="20"/>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="10"/>
@@ -1693,13 +1677,13 @@
       <c r="F51" s="8"/>
       <c r="G51" s="8"/>
       <c r="H51" s="8"/>
-      <c r="I51" s="44"/>
+      <c r="I51" s="39"/>
       <c r="J51" s="8"/>
       <c r="K51" s="8"/>
-      <c r="L51" s="19"/>
+      <c r="L51" s="16"/>
       <c r="M51" s="11"/>
-      <c r="N51" s="20"/>
-      <c r="O51" s="24"/>
+      <c r="N51" s="17"/>
+      <c r="O51" s="20"/>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="10"/>
@@ -1710,13 +1694,13 @@
       <c r="F52" s="8"/>
       <c r="G52" s="8"/>
       <c r="H52" s="8"/>
-      <c r="I52" s="44"/>
+      <c r="I52" s="39"/>
       <c r="J52" s="8"/>
       <c r="K52" s="8"/>
       <c r="L52" s="14"/>
       <c r="M52" s="7"/>
       <c r="N52" s="15"/>
-      <c r="O52" s="21"/>
+      <c r="O52" s="18"/>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="10"/>
@@ -1727,13 +1711,13 @@
       <c r="F53" s="8"/>
       <c r="G53" s="8"/>
       <c r="H53" s="8"/>
-      <c r="I53" s="44"/>
+      <c r="I53" s="39"/>
       <c r="J53" s="8"/>
       <c r="K53" s="8"/>
-      <c r="L53" s="19"/>
+      <c r="L53" s="16"/>
       <c r="M53" s="11"/>
-      <c r="N53" s="20"/>
-      <c r="O53" s="24"/>
+      <c r="N53" s="17"/>
+      <c r="O53" s="20"/>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="10"/>
@@ -1744,13 +1728,13 @@
       <c r="F54" s="8"/>
       <c r="G54" s="8"/>
       <c r="H54" s="8"/>
-      <c r="I54" s="44"/>
+      <c r="I54" s="39"/>
       <c r="J54" s="8"/>
       <c r="K54" s="8"/>
       <c r="L54" s="14"/>
       <c r="M54" s="7"/>
       <c r="N54" s="15"/>
-      <c r="O54" s="25"/>
+      <c r="O54" s="19"/>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="10"/>
@@ -1761,13 +1745,13 @@
       <c r="F55" s="8"/>
       <c r="G55" s="8"/>
       <c r="H55" s="8"/>
-      <c r="I55" s="44"/>
+      <c r="I55" s="39"/>
       <c r="J55" s="8"/>
       <c r="K55" s="8"/>
       <c r="L55" s="14"/>
       <c r="M55" s="7"/>
       <c r="N55" s="15"/>
-      <c r="O55" s="25"/>
+      <c r="O55" s="19"/>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="10"/>
@@ -1778,13 +1762,13 @@
       <c r="F56" s="8"/>
       <c r="G56" s="8"/>
       <c r="H56" s="8"/>
-      <c r="I56" s="44"/>
+      <c r="I56" s="39"/>
       <c r="J56" s="8"/>
       <c r="K56" s="8"/>
-      <c r="L56" s="16"/>
-      <c r="M56" s="17"/>
-      <c r="N56" s="18"/>
-      <c r="O56" s="23"/>
+      <c r="L56" s="14"/>
+      <c r="M56" s="7"/>
+      <c r="N56" s="15"/>
+      <c r="O56" s="19"/>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="10"/>
@@ -1795,13 +1779,13 @@
       <c r="F57" s="8"/>
       <c r="G57" s="8"/>
       <c r="H57" s="8"/>
-      <c r="I57" s="44"/>
+      <c r="I57" s="39"/>
       <c r="J57" s="8"/>
       <c r="K57" s="8"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="17"/>
-      <c r="N57" s="18"/>
-      <c r="O57" s="23"/>
+      <c r="L57" s="14"/>
+      <c r="M57" s="7"/>
+      <c r="N57" s="15"/>
+      <c r="O57" s="19"/>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="10"/>
@@ -1812,13 +1796,13 @@
       <c r="F58" s="8"/>
       <c r="G58" s="8"/>
       <c r="H58" s="8"/>
-      <c r="I58" s="44"/>
+      <c r="I58" s="39"/>
       <c r="J58" s="8"/>
       <c r="K58" s="8"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="17"/>
-      <c r="N58" s="18"/>
-      <c r="O58" s="23"/>
+      <c r="L58" s="14"/>
+      <c r="M58" s="7"/>
+      <c r="N58" s="15"/>
+      <c r="O58" s="19"/>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="13"/>
@@ -1829,13 +1813,13 @@
       <c r="F59" s="8"/>
       <c r="G59" s="8"/>
       <c r="H59" s="8"/>
-      <c r="I59" s="44"/>
+      <c r="I59" s="39"/>
       <c r="J59" s="8"/>
       <c r="K59" s="8"/>
-      <c r="L59" s="16"/>
-      <c r="M59" s="17"/>
-      <c r="N59" s="18"/>
-      <c r="O59" s="23"/>
+      <c r="L59" s="14"/>
+      <c r="M59" s="7"/>
+      <c r="N59" s="15"/>
+      <c r="O59" s="19"/>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="10"/>
@@ -1846,13 +1830,13 @@
       <c r="F60" s="8"/>
       <c r="G60" s="8"/>
       <c r="H60" s="8"/>
-      <c r="I60" s="44"/>
+      <c r="I60" s="39"/>
       <c r="J60" s="8"/>
       <c r="K60" s="8"/>
-      <c r="L60" s="16"/>
-      <c r="M60" s="17"/>
-      <c r="N60" s="18"/>
-      <c r="O60" s="23"/>
+      <c r="L60" s="14"/>
+      <c r="M60" s="7"/>
+      <c r="N60" s="15"/>
+      <c r="O60" s="19"/>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="10"/>
@@ -1863,13 +1847,13 @@
       <c r="F61" s="8"/>
       <c r="G61" s="8"/>
       <c r="H61" s="8"/>
-      <c r="I61" s="44"/>
+      <c r="I61" s="39"/>
       <c r="J61" s="8"/>
       <c r="K61" s="8"/>
-      <c r="L61" s="16"/>
-      <c r="M61" s="17"/>
-      <c r="N61" s="18"/>
-      <c r="O61" s="23"/>
+      <c r="L61" s="14"/>
+      <c r="M61" s="7"/>
+      <c r="N61" s="15"/>
+      <c r="O61" s="19"/>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="10"/>
@@ -1880,13 +1864,13 @@
       <c r="F62" s="8"/>
       <c r="G62" s="8"/>
       <c r="H62" s="8"/>
-      <c r="I62" s="44"/>
+      <c r="I62" s="39"/>
       <c r="J62" s="8"/>
       <c r="K62" s="8"/>
-      <c r="L62" s="16"/>
-      <c r="M62" s="17"/>
-      <c r="N62" s="18"/>
-      <c r="O62" s="23"/>
+      <c r="L62" s="14"/>
+      <c r="M62" s="7"/>
+      <c r="N62" s="15"/>
+      <c r="O62" s="19"/>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="10"/>
@@ -1897,13 +1881,13 @@
       <c r="F63" s="8"/>
       <c r="G63" s="8"/>
       <c r="H63" s="8"/>
-      <c r="I63" s="44"/>
+      <c r="I63" s="39"/>
       <c r="J63" s="8"/>
       <c r="K63" s="8"/>
-      <c r="L63" s="16"/>
-      <c r="M63" s="17"/>
-      <c r="N63" s="18"/>
-      <c r="O63" s="23"/>
+      <c r="L63" s="14"/>
+      <c r="M63" s="7"/>
+      <c r="N63" s="15"/>
+      <c r="O63" s="19"/>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="10"/>
@@ -1914,13 +1898,13 @@
       <c r="F64" s="8"/>
       <c r="G64" s="8"/>
       <c r="H64" s="8"/>
-      <c r="I64" s="44"/>
+      <c r="I64" s="39"/>
       <c r="J64" s="8"/>
       <c r="K64" s="8"/>
       <c r="L64" s="14"/>
       <c r="M64" s="7"/>
       <c r="N64" s="15"/>
-      <c r="O64" s="25"/>
+      <c r="O64" s="19"/>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="10"/>
@@ -1931,13 +1915,13 @@
       <c r="F65" s="8"/>
       <c r="G65" s="8"/>
       <c r="H65" s="8"/>
-      <c r="I65" s="44"/>
+      <c r="I65" s="39"/>
       <c r="J65" s="8"/>
       <c r="K65" s="8"/>
-      <c r="L65" s="16"/>
-      <c r="M65" s="17"/>
-      <c r="N65" s="18"/>
-      <c r="O65" s="23"/>
+      <c r="L65" s="14"/>
+      <c r="M65" s="7"/>
+      <c r="N65" s="15"/>
+      <c r="O65" s="19"/>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="10"/>
@@ -1948,13 +1932,13 @@
       <c r="F66" s="8"/>
       <c r="G66" s="8"/>
       <c r="H66" s="8"/>
-      <c r="I66" s="44"/>
+      <c r="I66" s="39"/>
       <c r="J66" s="8"/>
       <c r="K66" s="8"/>
-      <c r="L66" s="16"/>
-      <c r="M66" s="17"/>
-      <c r="N66" s="18"/>
-      <c r="O66" s="23"/>
+      <c r="L66" s="14"/>
+      <c r="M66" s="7"/>
+      <c r="N66" s="15"/>
+      <c r="O66" s="19"/>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="10"/>
@@ -1965,13 +1949,13 @@
       <c r="F67" s="8"/>
       <c r="G67" s="8"/>
       <c r="H67" s="8"/>
-      <c r="I67" s="44"/>
+      <c r="I67" s="39"/>
       <c r="J67" s="8"/>
       <c r="K67" s="8"/>
-      <c r="L67" s="16"/>
-      <c r="M67" s="17"/>
-      <c r="N67" s="18"/>
-      <c r="O67" s="23"/>
+      <c r="L67" s="14"/>
+      <c r="M67" s="7"/>
+      <c r="N67" s="15"/>
+      <c r="O67" s="19"/>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="10"/>
@@ -1982,13 +1966,13 @@
       <c r="F68" s="8"/>
       <c r="G68" s="8"/>
       <c r="H68" s="8"/>
-      <c r="I68" s="44"/>
+      <c r="I68" s="39"/>
       <c r="J68" s="8"/>
       <c r="K68" s="8"/>
-      <c r="L68" s="16"/>
-      <c r="M68" s="17"/>
-      <c r="N68" s="18"/>
-      <c r="O68" s="23"/>
+      <c r="L68" s="14"/>
+      <c r="M68" s="7"/>
+      <c r="N68" s="15"/>
+      <c r="O68" s="19"/>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="10"/>
@@ -1999,13 +1983,13 @@
       <c r="F69" s="8"/>
       <c r="G69" s="8"/>
       <c r="H69" s="8"/>
-      <c r="I69" s="44"/>
+      <c r="I69" s="39"/>
       <c r="J69" s="8"/>
       <c r="K69" s="8"/>
-      <c r="L69" s="16"/>
-      <c r="M69" s="17"/>
-      <c r="N69" s="18"/>
-      <c r="O69" s="23"/>
+      <c r="L69" s="14"/>
+      <c r="M69" s="7"/>
+      <c r="N69" s="15"/>
+      <c r="O69" s="19"/>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="10"/>
@@ -2016,13 +2000,13 @@
       <c r="F70" s="8"/>
       <c r="G70" s="8"/>
       <c r="H70" s="8"/>
-      <c r="I70" s="44"/>
+      <c r="I70" s="39"/>
       <c r="J70" s="8"/>
       <c r="K70" s="8"/>
-      <c r="L70" s="16"/>
-      <c r="M70" s="17"/>
-      <c r="N70" s="18"/>
-      <c r="O70" s="23"/>
+      <c r="L70" s="14"/>
+      <c r="M70" s="7"/>
+      <c r="N70" s="15"/>
+      <c r="O70" s="19"/>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="10"/>
@@ -2033,13 +2017,13 @@
       <c r="F71" s="8"/>
       <c r="G71" s="8"/>
       <c r="H71" s="8"/>
-      <c r="I71" s="44"/>
+      <c r="I71" s="39"/>
       <c r="J71" s="8"/>
       <c r="K71" s="8"/>
-      <c r="L71" s="16"/>
-      <c r="M71" s="17"/>
-      <c r="N71" s="18"/>
-      <c r="O71" s="23"/>
+      <c r="L71" s="14"/>
+      <c r="M71" s="7"/>
+      <c r="N71" s="15"/>
+      <c r="O71" s="19"/>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="10"/>
@@ -2050,13 +2034,13 @@
       <c r="F72" s="8"/>
       <c r="G72" s="8"/>
       <c r="H72" s="8"/>
-      <c r="I72" s="44"/>
+      <c r="I72" s="39"/>
       <c r="J72" s="8"/>
       <c r="K72" s="8"/>
       <c r="L72" s="14"/>
       <c r="M72" s="7"/>
       <c r="N72" s="15"/>
-      <c r="O72" s="21"/>
+      <c r="O72" s="18"/>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="10"/>
@@ -2067,13 +2051,13 @@
       <c r="F73" s="8"/>
       <c r="G73" s="8"/>
       <c r="H73" s="8"/>
-      <c r="I73" s="44"/>
+      <c r="I73" s="39"/>
       <c r="J73" s="8"/>
       <c r="K73" s="8"/>
       <c r="L73" s="14"/>
       <c r="M73" s="11"/>
-      <c r="N73" s="29"/>
-      <c r="O73" s="30"/>
+      <c r="N73" s="24"/>
+      <c r="O73" s="25"/>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="10"/>
@@ -2084,13 +2068,13 @@
       <c r="F74" s="8"/>
       <c r="G74" s="8"/>
       <c r="H74" s="8"/>
-      <c r="I74" s="44"/>
+      <c r="I74" s="39"/>
       <c r="J74" s="8"/>
       <c r="K74" s="8"/>
       <c r="L74" s="14"/>
       <c r="M74" s="11"/>
-      <c r="N74" s="29"/>
-      <c r="O74" s="30"/>
+      <c r="N74" s="24"/>
+      <c r="O74" s="25"/>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="10"/>
@@ -2101,13 +2085,13 @@
       <c r="F75" s="8"/>
       <c r="G75" s="8"/>
       <c r="H75" s="8"/>
-      <c r="I75" s="44"/>
+      <c r="I75" s="39"/>
       <c r="J75" s="8"/>
       <c r="K75" s="8"/>
       <c r="L75" s="14"/>
       <c r="M75" s="11"/>
-      <c r="N75" s="29"/>
-      <c r="O75" s="30"/>
+      <c r="N75" s="24"/>
+      <c r="O75" s="25"/>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="10"/>
@@ -2118,13 +2102,13 @@
       <c r="F76" s="8"/>
       <c r="G76" s="8"/>
       <c r="H76" s="8"/>
-      <c r="I76" s="44"/>
+      <c r="I76" s="39"/>
       <c r="J76" s="8"/>
       <c r="K76" s="8"/>
       <c r="L76" s="14"/>
       <c r="M76" s="11"/>
-      <c r="N76" s="29"/>
-      <c r="O76" s="30"/>
+      <c r="N76" s="24"/>
+      <c r="O76" s="25"/>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="10"/>
@@ -2135,13 +2119,13 @@
       <c r="F77" s="8"/>
       <c r="G77" s="8"/>
       <c r="H77" s="8"/>
-      <c r="I77" s="44"/>
+      <c r="I77" s="39"/>
       <c r="J77" s="8"/>
       <c r="K77" s="8"/>
       <c r="L77" s="14"/>
       <c r="M77" s="11"/>
-      <c r="N77" s="29"/>
-      <c r="O77" s="30"/>
+      <c r="N77" s="24"/>
+      <c r="O77" s="25"/>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="10"/>
@@ -2152,234 +2136,234 @@
       <c r="F78" s="8"/>
       <c r="G78" s="8"/>
       <c r="H78" s="8"/>
-      <c r="I78" s="44"/>
+      <c r="I78" s="39"/>
       <c r="J78" s="8"/>
       <c r="K78" s="8"/>
       <c r="L78" s="14"/>
       <c r="M78" s="11"/>
-      <c r="N78" s="29"/>
-      <c r="O78" s="30"/>
+      <c r="N78" s="24"/>
+      <c r="O78" s="25"/>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="10"/>
       <c r="B79" s="10"/>
-      <c r="C79" s="17"/>
+      <c r="C79" s="7"/>
       <c r="D79" s="8"/>
       <c r="E79" s="8"/>
       <c r="F79" s="8"/>
       <c r="G79" s="8"/>
       <c r="H79" s="8"/>
-      <c r="I79" s="44"/>
+      <c r="I79" s="39"/>
       <c r="J79" s="8"/>
       <c r="K79" s="8"/>
-      <c r="L79" s="16"/>
-      <c r="M79" s="17"/>
-      <c r="N79" s="18"/>
-      <c r="O79" s="23"/>
+      <c r="L79" s="14"/>
+      <c r="M79" s="7"/>
+      <c r="N79" s="15"/>
+      <c r="O79" s="19"/>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="10"/>
       <c r="B80" s="10"/>
-      <c r="C80" s="17"/>
+      <c r="C80" s="7"/>
       <c r="D80" s="8"/>
       <c r="E80" s="8"/>
       <c r="F80" s="8"/>
       <c r="G80" s="8"/>
       <c r="H80" s="8"/>
-      <c r="I80" s="44"/>
+      <c r="I80" s="39"/>
       <c r="J80" s="8"/>
       <c r="K80" s="8"/>
-      <c r="L80" s="16"/>
-      <c r="M80" s="17"/>
-      <c r="N80" s="18"/>
-      <c r="O80" s="23"/>
+      <c r="L80" s="14"/>
+      <c r="M80" s="7"/>
+      <c r="N80" s="15"/>
+      <c r="O80" s="19"/>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="10"/>
       <c r="B81" s="10"/>
-      <c r="C81" s="17"/>
+      <c r="C81" s="7"/>
       <c r="D81" s="8"/>
       <c r="E81" s="8"/>
       <c r="F81" s="8"/>
       <c r="G81" s="8"/>
       <c r="H81" s="8"/>
-      <c r="I81" s="44"/>
+      <c r="I81" s="39"/>
       <c r="J81" s="8"/>
       <c r="K81" s="8"/>
-      <c r="L81" s="16"/>
-      <c r="M81" s="17"/>
-      <c r="N81" s="18"/>
-      <c r="O81" s="23"/>
+      <c r="L81" s="14"/>
+      <c r="M81" s="7"/>
+      <c r="N81" s="15"/>
+      <c r="O81" s="19"/>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="10"/>
       <c r="B82" s="10"/>
-      <c r="C82" s="17"/>
+      <c r="C82" s="7"/>
       <c r="D82" s="8"/>
       <c r="E82" s="8"/>
       <c r="F82" s="8"/>
       <c r="G82" s="8"/>
       <c r="H82" s="8"/>
-      <c r="I82" s="44"/>
+      <c r="I82" s="39"/>
       <c r="J82" s="8"/>
       <c r="K82" s="8"/>
-      <c r="L82" s="16"/>
-      <c r="M82" s="17"/>
-      <c r="N82" s="18"/>
-      <c r="O82" s="23"/>
+      <c r="L82" s="14"/>
+      <c r="M82" s="7"/>
+      <c r="N82" s="15"/>
+      <c r="O82" s="19"/>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="10"/>
       <c r="B83" s="10"/>
-      <c r="C83" s="17"/>
+      <c r="C83" s="7"/>
       <c r="D83" s="8"/>
       <c r="E83" s="8"/>
       <c r="F83" s="8"/>
       <c r="G83" s="8"/>
       <c r="H83" s="8"/>
-      <c r="I83" s="44"/>
+      <c r="I83" s="39"/>
       <c r="J83" s="8"/>
       <c r="K83" s="8"/>
-      <c r="L83" s="16"/>
-      <c r="M83" s="17"/>
-      <c r="N83" s="18"/>
-      <c r="O83" s="23"/>
+      <c r="L83" s="14"/>
+      <c r="M83" s="7"/>
+      <c r="N83" s="15"/>
+      <c r="O83" s="19"/>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="10"/>
       <c r="B84" s="10"/>
-      <c r="C84" s="17"/>
+      <c r="C84" s="7"/>
       <c r="D84" s="8"/>
       <c r="E84" s="8"/>
       <c r="F84" s="8"/>
       <c r="G84" s="8"/>
       <c r="H84" s="8"/>
-      <c r="I84" s="44"/>
+      <c r="I84" s="39"/>
       <c r="J84" s="8"/>
       <c r="K84" s="8"/>
-      <c r="L84" s="16"/>
-      <c r="M84" s="17"/>
-      <c r="N84" s="18"/>
-      <c r="O84" s="23"/>
+      <c r="L84" s="14"/>
+      <c r="M84" s="7"/>
+      <c r="N84" s="15"/>
+      <c r="O84" s="19"/>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="10"/>
       <c r="B85" s="10"/>
-      <c r="C85" s="17"/>
+      <c r="C85" s="7"/>
       <c r="D85" s="8"/>
       <c r="E85" s="8"/>
       <c r="F85" s="8"/>
       <c r="G85" s="8"/>
       <c r="H85" s="8"/>
-      <c r="I85" s="44"/>
+      <c r="I85" s="39"/>
       <c r="J85" s="8"/>
       <c r="K85" s="8"/>
-      <c r="L85" s="16"/>
-      <c r="M85" s="17"/>
-      <c r="N85" s="18"/>
-      <c r="O85" s="23"/>
+      <c r="L85" s="14"/>
+      <c r="M85" s="7"/>
+      <c r="N85" s="15"/>
+      <c r="O85" s="19"/>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="10"/>
       <c r="B86" s="10"/>
-      <c r="C86" s="17"/>
+      <c r="C86" s="7"/>
       <c r="D86" s="8"/>
       <c r="E86" s="8"/>
       <c r="F86" s="8"/>
       <c r="G86" s="8"/>
       <c r="H86" s="8"/>
-      <c r="I86" s="44"/>
+      <c r="I86" s="39"/>
       <c r="J86" s="8"/>
       <c r="K86" s="8"/>
-      <c r="L86" s="16"/>
-      <c r="M86" s="17"/>
-      <c r="N86" s="18"/>
-      <c r="O86" s="23"/>
+      <c r="L86" s="14"/>
+      <c r="M86" s="7"/>
+      <c r="N86" s="15"/>
+      <c r="O86" s="19"/>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="10"/>
       <c r="B87" s="10"/>
-      <c r="C87" s="17"/>
+      <c r="C87" s="7"/>
       <c r="D87" s="8"/>
       <c r="E87" s="8"/>
       <c r="F87" s="8"/>
       <c r="G87" s="8"/>
       <c r="H87" s="8"/>
-      <c r="I87" s="44"/>
+      <c r="I87" s="39"/>
       <c r="J87" s="8"/>
       <c r="K87" s="8"/>
-      <c r="L87" s="16"/>
-      <c r="M87" s="17"/>
-      <c r="N87" s="18"/>
-      <c r="O87" s="23"/>
+      <c r="L87" s="14"/>
+      <c r="M87" s="7"/>
+      <c r="N87" s="15"/>
+      <c r="O87" s="19"/>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="10"/>
       <c r="B88" s="10"/>
-      <c r="C88" s="17"/>
+      <c r="C88" s="7"/>
       <c r="D88" s="8"/>
       <c r="E88" s="8"/>
       <c r="F88" s="8"/>
       <c r="G88" s="8"/>
       <c r="H88" s="8"/>
-      <c r="I88" s="44"/>
+      <c r="I88" s="39"/>
       <c r="J88" s="8"/>
       <c r="K88" s="8"/>
-      <c r="L88" s="16"/>
-      <c r="M88" s="17"/>
-      <c r="N88" s="18"/>
-      <c r="O88" s="23"/>
+      <c r="L88" s="14"/>
+      <c r="M88" s="7"/>
+      <c r="N88" s="15"/>
+      <c r="O88" s="19"/>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" s="10"/>
       <c r="B89" s="10"/>
-      <c r="C89" s="17"/>
+      <c r="C89" s="7"/>
       <c r="D89" s="8"/>
       <c r="E89" s="8"/>
       <c r="F89" s="8"/>
       <c r="G89" s="8"/>
       <c r="H89" s="8"/>
-      <c r="I89" s="44"/>
+      <c r="I89" s="39"/>
       <c r="J89" s="8"/>
       <c r="K89" s="8"/>
-      <c r="L89" s="16"/>
-      <c r="M89" s="17"/>
-      <c r="N89" s="18"/>
-      <c r="O89" s="23"/>
+      <c r="L89" s="14"/>
+      <c r="M89" s="7"/>
+      <c r="N89" s="15"/>
+      <c r="O89" s="19"/>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="10"/>
       <c r="B90" s="10"/>
-      <c r="C90" s="17"/>
+      <c r="C90" s="7"/>
       <c r="D90" s="8"/>
       <c r="E90" s="8"/>
       <c r="F90" s="8"/>
       <c r="G90" s="8"/>
       <c r="H90" s="8"/>
-      <c r="I90" s="44"/>
+      <c r="I90" s="39"/>
       <c r="J90" s="8"/>
       <c r="K90" s="8"/>
-      <c r="L90" s="16"/>
-      <c r="M90" s="17"/>
-      <c r="N90" s="18"/>
-      <c r="O90" s="23"/>
+      <c r="L90" s="14"/>
+      <c r="M90" s="7"/>
+      <c r="N90" s="15"/>
+      <c r="O90" s="19"/>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" s="10"/>
       <c r="B91" s="10"/>
-      <c r="C91" s="17"/>
+      <c r="C91" s="7"/>
       <c r="D91" s="8"/>
       <c r="E91" s="8"/>
       <c r="F91" s="8"/>
       <c r="G91" s="8"/>
       <c r="H91" s="8"/>
-      <c r="I91" s="44"/>
+      <c r="I91" s="39"/>
       <c r="J91" s="8"/>
       <c r="K91" s="8"/>
-      <c r="L91" s="16"/>
-      <c r="M91" s="17"/>
-      <c r="N91" s="18"/>
-      <c r="O91" s="23"/>
+      <c r="L91" s="14"/>
+      <c r="M91" s="7"/>
+      <c r="N91" s="15"/>
+      <c r="O91" s="19"/>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" s="10"/>
@@ -2390,13 +2374,13 @@
       <c r="F92" s="8"/>
       <c r="G92" s="8"/>
       <c r="H92" s="8"/>
-      <c r="I92" s="44"/>
+      <c r="I92" s="39"/>
       <c r="J92" s="8"/>
       <c r="K92" s="8"/>
-      <c r="L92" s="16"/>
-      <c r="M92" s="17"/>
-      <c r="N92" s="18"/>
-      <c r="O92" s="23"/>
+      <c r="L92" s="14"/>
+      <c r="M92" s="7"/>
+      <c r="N92" s="15"/>
+      <c r="O92" s="19"/>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" s="10"/>
@@ -2407,13 +2391,13 @@
       <c r="F93" s="8"/>
       <c r="G93" s="8"/>
       <c r="H93" s="8"/>
-      <c r="I93" s="44"/>
+      <c r="I93" s="39"/>
       <c r="J93" s="8"/>
       <c r="K93" s="8"/>
-      <c r="L93" s="16"/>
-      <c r="M93" s="17"/>
-      <c r="N93" s="18"/>
-      <c r="O93" s="23"/>
+      <c r="L93" s="14"/>
+      <c r="M93" s="7"/>
+      <c r="N93" s="15"/>
+      <c r="O93" s="19"/>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" s="10"/>
@@ -2424,13 +2408,13 @@
       <c r="F94" s="8"/>
       <c r="G94" s="8"/>
       <c r="H94" s="8"/>
-      <c r="I94" s="44"/>
+      <c r="I94" s="39"/>
       <c r="J94" s="8"/>
       <c r="K94" s="8"/>
-      <c r="L94" s="16"/>
-      <c r="M94" s="17"/>
-      <c r="N94" s="18"/>
-      <c r="O94" s="23"/>
+      <c r="L94" s="14"/>
+      <c r="M94" s="7"/>
+      <c r="N94" s="15"/>
+      <c r="O94" s="19"/>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" s="10"/>
@@ -2441,13 +2425,13 @@
       <c r="F95" s="8"/>
       <c r="G95" s="8"/>
       <c r="H95" s="8"/>
-      <c r="I95" s="44"/>
+      <c r="I95" s="39"/>
       <c r="J95" s="8"/>
       <c r="K95" s="8"/>
-      <c r="L95" s="16"/>
-      <c r="M95" s="17"/>
-      <c r="N95" s="18"/>
-      <c r="O95" s="23"/>
+      <c r="L95" s="14"/>
+      <c r="M95" s="7"/>
+      <c r="N95" s="15"/>
+      <c r="O95" s="19"/>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" s="10"/>
@@ -2458,13 +2442,13 @@
       <c r="F96" s="8"/>
       <c r="G96" s="8"/>
       <c r="H96" s="8"/>
-      <c r="I96" s="44"/>
+      <c r="I96" s="39"/>
       <c r="J96" s="8"/>
       <c r="K96" s="8"/>
-      <c r="L96" s="16"/>
-      <c r="M96" s="17"/>
-      <c r="N96" s="18"/>
-      <c r="O96" s="23"/>
+      <c r="L96" s="14"/>
+      <c r="M96" s="7"/>
+      <c r="N96" s="15"/>
+      <c r="O96" s="19"/>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" s="10"/>
@@ -2475,13 +2459,13 @@
       <c r="F97" s="8"/>
       <c r="G97" s="8"/>
       <c r="H97" s="8"/>
-      <c r="I97" s="44"/>
+      <c r="I97" s="39"/>
       <c r="J97" s="8"/>
       <c r="K97" s="8"/>
-      <c r="L97" s="16"/>
-      <c r="M97" s="17"/>
-      <c r="N97" s="18"/>
-      <c r="O97" s="23"/>
+      <c r="L97" s="14"/>
+      <c r="M97" s="7"/>
+      <c r="N97" s="15"/>
+      <c r="O97" s="19"/>
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" s="10"/>
@@ -2492,13 +2476,13 @@
       <c r="F98" s="8"/>
       <c r="G98" s="8"/>
       <c r="H98" s="8"/>
-      <c r="I98" s="44"/>
+      <c r="I98" s="39"/>
       <c r="J98" s="8"/>
       <c r="K98" s="8"/>
-      <c r="L98" s="16"/>
-      <c r="M98" s="17"/>
-      <c r="N98" s="18"/>
-      <c r="O98" s="23"/>
+      <c r="L98" s="14"/>
+      <c r="M98" s="7"/>
+      <c r="N98" s="15"/>
+      <c r="O98" s="19"/>
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" s="10"/>
@@ -2509,13 +2493,13 @@
       <c r="F99" s="8"/>
       <c r="G99" s="8"/>
       <c r="H99" s="8"/>
-      <c r="I99" s="44"/>
+      <c r="I99" s="39"/>
       <c r="J99" s="8"/>
       <c r="K99" s="8"/>
-      <c r="L99" s="16"/>
-      <c r="M99" s="17"/>
-      <c r="N99" s="18"/>
-      <c r="O99" s="23"/>
+      <c r="L99" s="14"/>
+      <c r="M99" s="7"/>
+      <c r="N99" s="15"/>
+      <c r="O99" s="19"/>
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" s="10"/>
@@ -2526,13 +2510,13 @@
       <c r="F100" s="8"/>
       <c r="G100" s="8"/>
       <c r="H100" s="8"/>
-      <c r="I100" s="44"/>
+      <c r="I100" s="39"/>
       <c r="J100" s="8"/>
       <c r="K100" s="8"/>
-      <c r="L100" s="16"/>
-      <c r="M100" s="17"/>
-      <c r="N100" s="18"/>
-      <c r="O100" s="23"/>
+      <c r="L100" s="14"/>
+      <c r="M100" s="7"/>
+      <c r="N100" s="15"/>
+      <c r="O100" s="19"/>
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" s="10"/>
@@ -2543,13 +2527,13 @@
       <c r="F101" s="8"/>
       <c r="G101" s="8"/>
       <c r="H101" s="8"/>
-      <c r="I101" s="44"/>
+      <c r="I101" s="39"/>
       <c r="J101" s="8"/>
       <c r="K101" s="8"/>
-      <c r="L101" s="16"/>
-      <c r="M101" s="17"/>
-      <c r="N101" s="18"/>
-      <c r="O101" s="23"/>
+      <c r="L101" s="14"/>
+      <c r="M101" s="7"/>
+      <c r="N101" s="15"/>
+      <c r="O101" s="19"/>
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102" s="10"/>
@@ -2560,13 +2544,13 @@
       <c r="F102" s="8"/>
       <c r="G102" s="8"/>
       <c r="H102" s="8"/>
-      <c r="I102" s="44"/>
+      <c r="I102" s="39"/>
       <c r="J102" s="8"/>
       <c r="K102" s="8"/>
-      <c r="L102" s="16"/>
-      <c r="M102" s="17"/>
-      <c r="N102" s="18"/>
-      <c r="O102" s="23"/>
+      <c r="L102" s="14"/>
+      <c r="M102" s="7"/>
+      <c r="N102" s="15"/>
+      <c r="O102" s="19"/>
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103" s="10"/>
@@ -2577,13 +2561,13 @@
       <c r="F103" s="8"/>
       <c r="G103" s="8"/>
       <c r="H103" s="8"/>
-      <c r="I103" s="44"/>
+      <c r="I103" s="39"/>
       <c r="J103" s="8"/>
       <c r="K103" s="8"/>
-      <c r="L103" s="16"/>
-      <c r="M103" s="17"/>
-      <c r="N103" s="18"/>
-      <c r="O103" s="23"/>
+      <c r="L103" s="14"/>
+      <c r="M103" s="7"/>
+      <c r="N103" s="15"/>
+      <c r="O103" s="19"/>
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104" s="10"/>
@@ -2594,81 +2578,81 @@
       <c r="F104" s="8"/>
       <c r="G104" s="8"/>
       <c r="H104" s="8"/>
-      <c r="I104" s="44"/>
+      <c r="I104" s="39"/>
       <c r="J104" s="8"/>
       <c r="K104" s="8"/>
-      <c r="L104" s="16"/>
-      <c r="M104" s="17"/>
-      <c r="N104" s="18"/>
-      <c r="O104" s="23"/>
+      <c r="L104" s="14"/>
+      <c r="M104" s="7"/>
+      <c r="N104" s="15"/>
+      <c r="O104" s="19"/>
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105" s="10"/>
-      <c r="B105" s="31"/>
+      <c r="B105" s="26"/>
       <c r="C105" s="5"/>
       <c r="D105" s="8"/>
       <c r="E105" s="8"/>
       <c r="F105" s="8"/>
       <c r="G105" s="8"/>
       <c r="H105" s="8"/>
-      <c r="I105" s="44"/>
+      <c r="I105" s="39"/>
       <c r="J105" s="8"/>
       <c r="K105" s="8"/>
-      <c r="L105" s="16"/>
-      <c r="M105" s="17"/>
-      <c r="N105" s="18"/>
-      <c r="O105" s="23"/>
+      <c r="L105" s="14"/>
+      <c r="M105" s="7"/>
+      <c r="N105" s="15"/>
+      <c r="O105" s="19"/>
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106" s="10"/>
-      <c r="B106" s="32"/>
-      <c r="C106" s="26"/>
+      <c r="B106" s="27"/>
+      <c r="C106" s="21"/>
       <c r="D106" s="8"/>
       <c r="E106" s="8"/>
       <c r="F106" s="8"/>
       <c r="G106" s="8"/>
       <c r="H106" s="8"/>
-      <c r="I106" s="44"/>
+      <c r="I106" s="39"/>
       <c r="J106" s="8"/>
       <c r="K106" s="8"/>
-      <c r="L106" s="16"/>
-      <c r="M106" s="17"/>
-      <c r="N106" s="18"/>
-      <c r="O106" s="23"/>
+      <c r="L106" s="14"/>
+      <c r="M106" s="7"/>
+      <c r="N106" s="15"/>
+      <c r="O106" s="19"/>
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107" s="10"/>
       <c r="B107" s="10"/>
       <c r="C107" s="11"/>
       <c r="D107" s="8"/>
-      <c r="E107" s="27"/>
-      <c r="F107" s="27"/>
+      <c r="E107" s="22"/>
+      <c r="F107" s="22"/>
       <c r="G107" s="8"/>
       <c r="H107" s="8"/>
-      <c r="I107" s="44"/>
+      <c r="I107" s="39"/>
       <c r="J107" s="8"/>
       <c r="K107" s="8"/>
       <c r="L107" s="14"/>
       <c r="M107" s="11"/>
-      <c r="N107" s="29"/>
-      <c r="O107" s="30"/>
+      <c r="N107" s="24"/>
+      <c r="O107" s="25"/>
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108" s="10"/>
       <c r="B108" s="10"/>
       <c r="C108" s="9"/>
       <c r="D108" s="8"/>
-      <c r="E108" s="28"/>
-      <c r="F108" s="28"/>
+      <c r="E108" s="23"/>
+      <c r="F108" s="23"/>
       <c r="G108" s="8"/>
       <c r="H108" s="8"/>
-      <c r="I108" s="44"/>
+      <c r="I108" s="39"/>
       <c r="J108" s="8"/>
       <c r="K108" s="8"/>
       <c r="L108" s="14"/>
       <c r="M108" s="7"/>
       <c r="N108" s="15"/>
-      <c r="O108" s="21"/>
+      <c r="O108" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.3" footer="0.3"/>
